--- a/output/pdf_financials_xlsx/PTU.xlsx
+++ b/output/pdf_financials_xlsx/PTU.xlsx
@@ -1077,52 +1077,52 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.021044</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013032</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005438</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000237</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001384</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006062</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007437</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009124</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008616</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001273</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005305</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.046884</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06525499999999999</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09381200000000001</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.070323</v>
       </c>
     </row>
     <row r="13">
@@ -2102,52 +2102,52 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.262444</v>
+        <v>-2.2414</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.192195</v>
+        <v>-1.179163</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.969599</v>
+        <v>-1.964161</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.818673</v>
+        <v>-0.8184360000000001</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.317873</v>
+        <v>-1.317573</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.312775</v>
+        <v>-1.311391</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.620859</v>
+        <v>-1.614797</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.774134</v>
+        <v>-1.766697</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.40652</v>
+        <v>-1.397396</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.35048</v>
+        <v>-1.341864</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.456095</v>
+        <v>-1.454822</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-6.121594</v>
+        <v>-6.116289</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.353143</v>
+        <v>-6.306259</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.171302</v>
+        <v>-5.106047</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-5.155898</v>
+        <v>-5.062086</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-6.698469</v>
+        <v>-6.628146</v>
       </c>
     </row>
     <row r="28">
@@ -2228,52 +2228,52 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.228369</v>
+        <v>-2.207325</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.16471</v>
+        <v>-1.151678</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.947563</v>
+        <v>-1.942125</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.802938</v>
+        <v>-0.802701</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.307708</v>
+        <v>-1.307408</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.305433</v>
+        <v>-1.304049</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.618451</v>
+        <v>-1.612389</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.772664</v>
+        <v>-1.765227</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.404824</v>
+        <v>-1.3957</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.314553</v>
+        <v>-1.305937</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.420306</v>
+        <v>-1.419033</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-6.08591</v>
+        <v>-6.080605</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.317991</v>
+        <v>-6.271107</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-5.135851</v>
+        <v>-5.070596</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-5.120495</v>
+        <v>-5.026683</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-6.646997</v>
+        <v>-6.576674</v>
       </c>
     </row>
     <row r="30">
@@ -2549,40 +2549,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.025171</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.027139</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.027139</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.03917</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.683505</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.653467</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.002074</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.356026</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.618459</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.527116</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.150972</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.24455</v>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
@@ -2590,19 +2590,19 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>4.27557</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.925659</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>4.054315</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.241398</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>4.833675</v>
       </c>
     </row>
     <row r="35">
@@ -2675,40 +2675,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3.104423</v>
+        <v>3.129594</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.042172</v>
+        <v>2.069311</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.042172</v>
+        <v>2.069311</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.611658</v>
+        <v>1.650828</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.021696</v>
+        <v>0.705201</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.021929</v>
+        <v>1.675396</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.002074</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.356026</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.256055</v>
+        <v>1.874514</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.210706</v>
+        <v>2.737822</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.705101</v>
+        <v>1.856073</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.203825</v>
+        <v>1.448375</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -2716,19 +2716,19 @@
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>4.27557</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3.925659</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>4.054315</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2.241398</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>4.833675</v>
       </c>
     </row>
     <row r="37">
@@ -3431,40 +3431,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.101239</v>
+        <v>0.076068</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.07815</v>
+        <v>0.051011</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.07815</v>
+        <v>0.051011</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.160727</v>
+        <v>0.121557</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.865546</v>
+        <v>0.182041</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.701166</v>
+        <v>0.047699</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.282347</v>
+        <v>0.280273</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.470634</v>
+        <v>0.114608</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.095751</v>
+        <v>0.477292</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.952759</v>
+        <v>0.425643</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.261943</v>
+        <v>0.110971</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.35841</v>
+        <v>0.11386</v>
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
@@ -3472,19 +3472,19 @@
         </is>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.434275</v>
+        <v>0.158705</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>4.320927</v>
+        <v>0.395268</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>4.302107</v>
+        <v>0.247792</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.514539</v>
+        <v>0.273141</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>5.086843</v>
+        <v>0.253168</v>
       </c>
     </row>
     <row r="49">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -31102,7 +31102,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -38346,7 +38346,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -39846,7 +39846,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -41026,7 +41026,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -43052,7 +43052,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -45294,7 +45294,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">

--- a/output/pdf_financials_xlsx/PTU.xlsx
+++ b/output/pdf_financials_xlsx/PTU.xlsx
@@ -7628,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.010378</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -26540,7 +26540,11 @@
           <t>Proceeds from disposition of property and equipment 10,378</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PTU.xlsx
+++ b/output/pdf_financials_xlsx/PTU.xlsx
@@ -7628,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0.010378</v>
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -26540,11 +26540,7 @@
           <t>Proceeds from disposition of property and equipment 10,378</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -27394,7 +27390,11 @@
           <t>Fair value of broker warrants issued under private placement $</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
